--- a/AtchisonRegime/Outputs/USA/USA500/df_regSettingsUSA500.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_regSettingsUSA500.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I696"/>
+  <dimension ref="A1:I697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23061,7 +23061,7 @@
         <v>-1.113652454430497</v>
       </c>
       <c r="C686" t="n">
-        <v>0.006266379198084816</v>
+        <v>-0.01570867082860625</v>
       </c>
       <c r="D686" t="b">
         <v>0</v>
@@ -23094,7 +23094,7 @@
         <v>-1.13653593688915</v>
       </c>
       <c r="C687" t="n">
-        <v>0.02240605369896704</v>
+        <v>0.005131485533573125</v>
       </c>
       <c r="D687" t="b">
         <v>0</v>
@@ -23127,7 +23127,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="C688" t="n">
-        <v>0.05890779434252914</v>
+        <v>0.04460226520446691</v>
       </c>
       <c r="D688" t="b">
         <v>0</v>
@@ -23160,7 +23160,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C689" t="n">
-        <v>0.1365357185829741</v>
+        <v>0.10691331821946</v>
       </c>
       <c r="D689" t="b">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C690" t="n">
-        <v>0.19626538484902</v>
+        <v>0.1742576329953394</v>
       </c>
       <c r="D690" t="b">
         <v>0</v>
@@ -23226,7 +23226,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C691" t="n">
-        <v>0.2479141243562677</v>
+        <v>0.2230893786343014</v>
       </c>
       <c r="D691" t="b">
         <v>0</v>
@@ -23259,7 +23259,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C692" t="n">
-        <v>0.2597235153389927</v>
+        <v>0.2419933628466199</v>
       </c>
       <c r="D692" t="b">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C693" t="n">
-        <v>0.2098083315261438</v>
+        <v>0.2090047006632499</v>
       </c>
       <c r="D693" t="b">
         <v>0</v>
@@ -23325,7 +23325,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C694" t="n">
-        <v>0.1536160686024298</v>
+        <v>0.1277646818410845</v>
       </c>
       <c r="D694" t="b">
         <v>0</v>
@@ -23355,10 +23355,10 @@
         <v>45716</v>
       </c>
       <c r="B695" t="n">
-        <v>-0.8167702922088305</v>
+        <v>-0.8165764810113098</v>
       </c>
       <c r="C695" t="n">
-        <v>0.04657800836005581</v>
+        <v>0.03018097094312175</v>
       </c>
       <c r="D695" t="b">
         <v>0</v>
@@ -23388,10 +23388,10 @@
         <v>45747</v>
       </c>
       <c r="B696" t="n">
-        <v>-0.7844280456827043</v>
+        <v>-0.836774216411349</v>
       </c>
       <c r="C696" t="n">
-        <v>0</v>
+        <v>-0.04969816765883398</v>
       </c>
       <c r="D696" t="b">
         <v>0</v>
@@ -23411,6 +23411,39 @@
         </is>
       </c>
       <c r="I696" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B697" t="n">
+        <v>-0.879407738343786</v>
+      </c>
+      <c r="C697" t="n">
+        <v>-0.07980487945422567</v>
+      </c>
+      <c r="D697" t="b">
+        <v>0</v>
+      </c>
+      <c r="E697" t="b">
+        <v>1</v>
+      </c>
+      <c r="F697" t="n">
+        <v>-1.03916032741589</v>
+      </c>
+      <c r="G697" t="n">
+        <v>29845950.55070484</v>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
         <is>
           <t>Type 1</t>
         </is>

--- a/AtchisonRegime/Outputs/USA/USA500/df_regSettingsUSA500.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_regSettingsUSA500.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I697"/>
+  <dimension ref="A1:I698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23094,7 +23094,7 @@
         <v>-1.13653593688915</v>
       </c>
       <c r="C687" t="n">
-        <v>0.005131485533573125</v>
+        <v>0.06227684249567139</v>
       </c>
       <c r="D687" t="b">
         <v>0</v>
@@ -23127,7 +23127,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="C688" t="n">
-        <v>0.04460226520446691</v>
+        <v>0.04556975254307176</v>
       </c>
       <c r="D688" t="b">
         <v>0</v>
@@ -23160,7 +23160,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C689" t="n">
-        <v>0.10691331821946</v>
+        <v>0.1052335655208562</v>
       </c>
       <c r="D689" t="b">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C690" t="n">
-        <v>0.1742576329953394</v>
+        <v>0.1728209275757697</v>
       </c>
       <c r="D690" t="b">
         <v>0</v>
@@ -23226,7 +23226,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C691" t="n">
-        <v>0.2230893786343014</v>
+        <v>0.2184151007630489</v>
       </c>
       <c r="D691" t="b">
         <v>0</v>
@@ -23259,7 +23259,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C692" t="n">
-        <v>0.2419933628466199</v>
+        <v>0.2303545000567671</v>
       </c>
       <c r="D692" t="b">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C693" t="n">
-        <v>0.2090047006632499</v>
+        <v>0.1835149024713215</v>
       </c>
       <c r="D693" t="b">
         <v>0</v>
@@ -23325,7 +23325,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C694" t="n">
-        <v>0.1277646818410845</v>
+        <v>0.08173255609690118</v>
       </c>
       <c r="D694" t="b">
         <v>0</v>
@@ -23358,7 +23358,7 @@
         <v>-0.8165764810113098</v>
       </c>
       <c r="C695" t="n">
-        <v>0.03018097094312175</v>
+        <v>-0.0287673040728554</v>
       </c>
       <c r="D695" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>-0.836774216411349</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.04969816765883398</v>
+        <v>-0.1130750000232564</v>
       </c>
       <c r="D696" t="b">
         <v>0</v>
@@ -23421,35 +23421,355 @@
         <v>45777</v>
       </c>
       <c r="B697" t="n">
-        <v>-0.879407738343786</v>
+        <v>-0.8897447119737403</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.07980487945422567</v>
+        <v>-0.1320340448907042</v>
       </c>
       <c r="D697" t="b">
         <v>0</v>
       </c>
       <c r="E697" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F697" t="n">
-        <v>-1.03916032741589</v>
+        <v>-3.29503921298769</v>
       </c>
       <c r="G697" t="n">
-        <v>29845950.55070484</v>
+        <v>29165592.03828806</v>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>Type 1</t>
+          <t>Type 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" s="2" t="n">
+        <v>45808</v>
+      </c>
+      <c r="B698" t="n">
+        <v>-0.92790417568146</v>
+      </c>
+      <c r="C698" t="n">
+        <v>-0.07173289590007452</v>
+      </c>
+      <c r="D698" t="b">
+        <v>0</v>
+      </c>
+      <c r="E698" t="b">
+        <v>0</v>
+      </c>
+      <c r="F698" t="n">
+        <v>5.64090165380499</v>
+      </c>
+      <c r="G698" t="n">
+        <v>30810794.40191787</v>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005C6577D0C3AE724BBB504F46D5A19401" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="17afb16e0fbe716d3dcf2481b32b5550">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df76e320-99cb-4a11-b59f-8bf32867ab70" xmlns:ns3="c0789f30-979e-497b-8344-faefb3987540" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f6d0bb8d4e6a5d6b988ea2ed2503dbb5" ns2:_="" ns3:_="">
+    <xsd:import namespace="df76e320-99cb-4a11-b59f-8bf32867ab70"/>
+    <xsd:import namespace="c0789f30-979e-497b-8344-faefb3987540"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="df76e320-99cb-4a11-b59f-8bf32867ab70" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2ea5f6a7-5373-4784-9cd5-4ca8be386d98" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c0789f30-979e-497b-8344-faefb3987540" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f1100522-260f-4f17-9a31-47a12622b1e0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="c0789f30-979e-497b-8344-faefb3987540">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c0789f30-979e-497b-8344-faefb3987540" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="df76e320-99cb-4a11-b59f-8bf32867ab70">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E898B93-A392-4CE2-BDA0-AC70BB727CC2}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EE83FB6-3D3F-42CC-8726-389E8643E261}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FD6037D-7E5D-442E-AFC7-2005AB4B1F9C}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/USA500/df_regSettingsUSA500.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_regSettingsUSA500.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I698"/>
+  <dimension ref="A1:I699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23127,7 +23127,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="C688" t="n">
-        <v>0.04556975254307176</v>
+        <v>-0.05308453772626753</v>
       </c>
       <c r="D688" t="b">
         <v>0</v>
@@ -23160,7 +23160,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C689" t="n">
-        <v>0.1052335655208562</v>
+        <v>0.0994786913169827</v>
       </c>
       <c r="D689" t="b">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C690" t="n">
-        <v>0.1728209275757697</v>
+        <v>0.1578384480173436</v>
       </c>
       <c r="D690" t="b">
         <v>0</v>
@@ -23226,7 +23226,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C691" t="n">
-        <v>0.2184151007630489</v>
+        <v>0.1952250955118413</v>
       </c>
       <c r="D691" t="b">
         <v>0</v>
@@ -23259,7 +23259,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C692" t="n">
-        <v>0.2303545000567671</v>
+        <v>0.2218361370592049</v>
       </c>
       <c r="D692" t="b">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C693" t="n">
-        <v>0.1835149024713215</v>
+        <v>0.1720865300651815</v>
       </c>
       <c r="D693" t="b">
         <v>0</v>
@@ -23325,7 +23325,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C694" t="n">
-        <v>0.08173255609690118</v>
+        <v>0.08226213606388882</v>
       </c>
       <c r="D694" t="b">
         <v>0</v>
@@ -23358,7 +23358,7 @@
         <v>-0.8165764810113098</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.0287673040728554</v>
+        <v>-0.01714362521200617</v>
       </c>
       <c r="D695" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>-0.836774216411349</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.1130750000232564</v>
+        <v>-0.05274704393562812</v>
       </c>
       <c r="D696" t="b">
         <v>0</v>
@@ -23424,7 +23424,7 @@
         <v>-0.8897447119737403</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.1320340448907042</v>
+        <v>-0.0352985940476525</v>
       </c>
       <c r="D697" t="b">
         <v>0</v>
@@ -23433,10 +23433,10 @@
         <v>0</v>
       </c>
       <c r="F697" t="n">
-        <v>-3.29503921298769</v>
+        <v>-2.92395629121986</v>
       </c>
       <c r="G697" t="n">
-        <v>29165592.03828806</v>
+        <v>29277508.25251923</v>
       </c>
       <c r="H697" t="inlineStr">
         <is>
@@ -23457,7 +23457,7 @@
         <v>-0.92790417568146</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.07173289590007452</v>
+        <v>0.0692095874542254</v>
       </c>
       <c r="D698" t="b">
         <v>0</v>
@@ -23466,10 +23466,10 @@
         <v>0</v>
       </c>
       <c r="F698" t="n">
-        <v>5.64090165380499</v>
+        <v>8.793936915663391</v>
       </c>
       <c r="G698" t="n">
-        <v>30810794.40191787</v>
+        <v>31852153.85872392</v>
       </c>
       <c r="H698" t="inlineStr">
         <is>
@@ -23477,6 +23477,39 @@
         </is>
       </c>
       <c r="I698" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B699" t="n">
+        <v>-0.9151477448940367</v>
+      </c>
+      <c r="C699" t="n">
+        <v>0.1501696003153849</v>
+      </c>
+      <c r="D699" t="b">
+        <v>0</v>
+      </c>
+      <c r="E699" t="b">
+        <v>0</v>
+      </c>
+      <c r="F699" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="G699" t="n">
+        <v>34653212.17534014</v>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
         <is>
           <t>Type 3</t>
         </is>
@@ -23763,13 +23796,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3E898B93-A392-4CE2-BDA0-AC70BB727CC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C285B9A6-5DAA-44CF-A721-A60CD200197D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EE83FB6-3D3F-42CC-8726-389E8643E261}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA60EB6-74ED-489A-A920-69D6F455F57F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FD6037D-7E5D-442E-AFC7-2005AB4B1F9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B461090-234E-4D70-A630-7D930F54A5F3}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/USA500/df_regSettingsUSA500.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_regSettingsUSA500.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I699"/>
+  <dimension ref="A1:I702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23160,7 +23160,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C689" t="n">
-        <v>0.0994786913169827</v>
+        <v>0.05734064607590641</v>
       </c>
       <c r="D689" t="b">
         <v>0</v>
@@ -23193,7 +23193,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C690" t="n">
-        <v>0.1578384480173436</v>
+        <v>0.1339068761472364</v>
       </c>
       <c r="D690" t="b">
         <v>0</v>
@@ -23226,7 +23226,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C691" t="n">
-        <v>0.1952250955118413</v>
+        <v>0.2044769373519747</v>
       </c>
       <c r="D691" t="b">
         <v>0</v>
@@ -23259,7 +23259,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C692" t="n">
-        <v>0.2218361370592049</v>
+        <v>0.2187455920969442</v>
       </c>
       <c r="D692" t="b">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C693" t="n">
-        <v>0.1720865300651815</v>
+        <v>0.1768205626204333</v>
       </c>
       <c r="D693" t="b">
         <v>0</v>
@@ -23325,7 +23325,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C694" t="n">
-        <v>0.08226213606388882</v>
+        <v>0.08073394575470391</v>
       </c>
       <c r="D694" t="b">
         <v>0</v>
@@ -23358,7 +23358,7 @@
         <v>-0.8165764810113098</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.01714362521200617</v>
+        <v>-0.02131999920992771</v>
       </c>
       <c r="D695" t="b">
         <v>0</v>
@@ -23391,7 +23391,7 @@
         <v>-0.836774216411349</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.05274704393562812</v>
+        <v>-0.09131494158003906</v>
       </c>
       <c r="D696" t="b">
         <v>0</v>
@@ -23424,7 +23424,7 @@
         <v>-0.8897447119737403</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.0352985940476525</v>
+        <v>-0.08636672660505716</v>
       </c>
       <c r="D697" t="b">
         <v>0</v>
@@ -23454,10 +23454,10 @@
         <v>45808</v>
       </c>
       <c r="B698" t="n">
-        <v>-0.92790417568146</v>
+        <v>-0.9219801244493988</v>
       </c>
       <c r="C698" t="n">
-        <v>0.0692095874542254</v>
+        <v>0.00433402541888157</v>
       </c>
       <c r="D698" t="b">
         <v>0</v>
@@ -23487,10 +23487,10 @@
         <v>45838</v>
       </c>
       <c r="B699" t="n">
-        <v>-0.9151477448940367</v>
+        <v>-0.8555726940035157</v>
       </c>
       <c r="C699" t="n">
-        <v>0.1501696003153849</v>
+        <v>0.07493456856087748</v>
       </c>
       <c r="D699" t="b">
         <v>0</v>
@@ -23512,6 +23512,105 @@
       <c r="I699" t="inlineStr">
         <is>
           <t>Type 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="B700" t="n">
+        <v>-0.7604670143878566</v>
+      </c>
+      <c r="C700" t="n">
+        <v>0.08295756118067453</v>
+      </c>
+      <c r="D700" t="b">
+        <v>0</v>
+      </c>
+      <c r="E700" t="b">
+        <v>1</v>
+      </c>
+      <c r="F700" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="G700" t="n">
+        <v>37700593.79329053</v>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="B701" t="n">
+        <v>-0.6264616369049143</v>
+      </c>
+      <c r="C701" t="n">
+        <v>0.0646752787274633</v>
+      </c>
+      <c r="D701" t="b">
+        <v>0</v>
+      </c>
+      <c r="E701" t="b">
+        <v>1</v>
+      </c>
+      <c r="F701" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="G701" t="n">
+        <v>41015960.22830301</v>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B702" t="n">
+        <v>-0.5470797216326779</v>
+      </c>
+      <c r="C702" t="n">
+        <v>0.05674426346513629</v>
+      </c>
+      <c r="D702" t="b">
+        <v>0</v>
+      </c>
+      <c r="E702" t="b">
+        <v>1</v>
+      </c>
+      <c r="F702" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="G702" t="n">
+        <v>44622877.89613356</v>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
@@ -23796,13 +23895,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C285B9A6-5DAA-44CF-A721-A60CD200197D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3960ABA6-E9DE-4FC1-9B8F-3B101543D250}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FA60EB6-74ED-489A-A920-69D6F455F57F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CAED96E-5D59-4AB0-BC8D-872AE8847B79}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B461090-234E-4D70-A630-7D930F54A5F3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A9B950-A069-4517-AD9B-90B0D9251ED3}"/>
 </file>